--- a/Result/profitability/2540.xlsx
+++ b/Result/profitability/2540.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01750000000000002</v>
+        <v>-0.06999999999999995</v>
       </c>
       <c r="N2" t="n">
-        <v>19.04125000000001</v>
+        <v>17.22375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.30125</v>
+        <v>-0.3574999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.5775</v>
+        <v>16.06625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.05249999999999994</v>
       </c>
       <c r="N4" t="n">
-        <v>14.08375</v>
+        <v>14.32125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>7.93</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9349999999999999</v>
+        <v>0.82625</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.112499999999995</v>
+        <v>-6.031249999999995</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.95</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7037499999999999</v>
+        <v>0.7125</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.219999999999995</v>
+        <v>-6.084999999999995</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.56375</v>
+        <v>0.5662500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.443749999999996</v>
+        <v>-7.459999999999994</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4125</v>
+        <v>0.4175000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.506249999999994</v>
+        <v>-8.066249999999995</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.35375</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.922499999999997</v>
+        <v>-7.922499999999995</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.5299999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.363749999999997</v>
+        <v>-7.363749999999995</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>-0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2737499999999999</v>
+        <v>0.27375</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
@@ -9778,6 +9778,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1612</v>
+      </c>
+      <c r="E75" t="n">
+        <v>408</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>81</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-38</v>
+      </c>
+      <c r="J75" t="n">
+        <v>43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.63125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2112845138055222</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.350000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2669814747548129</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
